--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>1/9</t>
         </is>
       </c>
     </row>
@@ -723,60 +731,64 @@
       <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -790,7 +802,7 @@
       <c r="T3" s="2" t="inlineStr"/>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>2/9</t>
         </is>
       </c>
     </row>
@@ -834,7 +850,7 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -844,7 +860,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -887,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -901,7 +917,7 @@
       <c r="T4" s="2" t="inlineStr"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -937,7 +953,911 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>80分钟</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>3/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,24 +642,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -870,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -991,24 +999,24 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1018,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/9</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1183,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1211,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1244,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,33 +1280,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/12</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1405,7 +1421,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1515,12 +1531,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1631,7 +1647,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1742,7 +1758,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1750,22 +1766,22 @@
       <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1798,12 +1814,12 @@
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1852,12 +1868,801 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>79.0</t>
         </is>
       </c>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>2/9</t>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>3/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1108,32 +1108,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1141,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1165,17 +1169,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1185,13 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1371,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1482,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1597,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1708,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1819,7 +1827,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1934,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2049,7 +2057,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2160,7 +2168,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2275,7 +2283,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2319,13 +2327,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/12</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2398,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2497,7 +2509,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2624,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC19"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1237,24 +1237,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1346,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1379,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1403,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1457,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1490,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,37 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1572,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -1605,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1629,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1683,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -1716,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1740,33 +1764,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1794,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -1827,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1851,37 +1883,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1974,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1981,7 +2013,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -1996,7 +2028,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2107,7 +2139,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2222,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2283,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2337,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2448,7 +2480,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2558,12 +2590,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2674,7 +2706,919 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1844,12 +1844,12 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1941,32 +1941,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1974,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1998,17 +2002,17 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -2018,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2056,32 +2060,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -2089,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2113,33 +2121,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2167,32 +2179,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2200,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2224,37 +2240,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2282,32 +2298,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2315,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2339,17 +2359,17 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
@@ -2359,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2397,32 +2417,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -2430,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2454,33 +2478,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2508,32 +2536,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2541,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2565,37 +2597,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2623,32 +2655,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -2656,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2680,33 +2716,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2734,32 +2774,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -2767,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2791,33 +2835,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2845,32 +2893,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -2878,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2902,33 +2954,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2989,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3043,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3143,7 +3199,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3158,7 +3214,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3273,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3378,17 +3434,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3503,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3511,22 +3567,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3559,12 +3615,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3578,47 +3634,967 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
+      <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
         </is>
       </c>
-      <c r="AC27" s="2" t="inlineStr">
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,17 +2493,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2784,24 +2784,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3012,32 +3012,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3045,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3069,32 +3073,32 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3127,32 +3131,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3160,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,17 +3192,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3204,12 +3212,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3242,32 +3250,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3275,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3299,17 +3311,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3319,17 +3331,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3357,32 +3369,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3390,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3414,32 +3430,32 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3472,32 +3488,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -3505,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3529,37 +3549,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3702,32 +3722,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3735,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3759,37 +3783,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3817,32 +3841,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -3850,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3874,32 +3902,32 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3932,32 +3960,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -3965,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3989,37 +4021,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4047,32 +4079,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4080,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4104,17 +4140,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4124,12 +4160,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4195,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4310,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4349,7 +4385,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4425,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4469,12 +4505,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4540,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4589,10 +4625,815 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
         <is>
           <t>7/14</t>
         </is>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,14 +1184,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>79.5</t>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,14 +2374,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>79.5</t>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,22 +2850,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3803,17 +3803,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3851,24 +3851,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3970,24 +3970,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4089,24 +4089,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4198,32 +4198,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4231,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4255,37 +4259,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4313,32 +4317,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -4346,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4370,17 +4378,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4390,17 +4398,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -4428,32 +4436,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4461,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4485,17 +4497,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4505,17 +4517,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -4543,32 +4555,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -4576,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4600,37 +4616,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4658,32 +4674,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -4691,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,17 +4735,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4735,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4773,32 +4793,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4806,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,37 +4854,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4888,32 +4912,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4921,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4945,17 +4973,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4965,17 +4993,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5036,7 +5064,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5085,12 +5113,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5190,7 +5218,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5205,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5310,17 +5338,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5430,12 +5458,698 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,14 +1660,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,17 +2493,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,14 +3326,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,17 +3917,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4815,12 +4815,12 @@
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4922,19 +4922,19 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5031,32 +5031,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -5064,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5088,17 +5092,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5108,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5146,32 +5150,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5179,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5203,17 +5211,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5223,17 +5231,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5261,32 +5269,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -5294,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5318,17 +5330,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5338,12 +5350,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5376,32 +5388,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -5409,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5433,32 +5449,32 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5524,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5578,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,7 +5694,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5693,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5808,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5908,7 +5924,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5980,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6024,17 +6040,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6153,6 +6169,577 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,17 +1422,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,17 +2374,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5507,32 +5507,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5540,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5564,17 +5568,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5584,17 +5588,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5622,32 +5626,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -5655,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5679,17 +5687,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5699,12 +5707,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5737,32 +5745,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5770,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5794,32 +5806,32 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5852,32 +5864,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -5885,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5909,17 +5925,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5929,13 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5963,32 +5983,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5996,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6020,37 +6044,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6078,32 +6102,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6111,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6135,32 +6163,32 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6226,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6275,12 +6303,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6380,7 +6408,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6456,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6500,12 +6528,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6571,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6625,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6714,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6730,13 +6758,592 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB53" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>81.7</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>81.8</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>80.6</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC58"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5993,24 +5993,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6221,32 +6221,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -6254,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6278,17 +6282,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6298,12 +6302,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6369,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6484,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6599,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6638,7 +6642,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6714,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6829,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6944,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7059,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7174,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7223,7 +7227,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7236,22 +7240,22 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7284,12 +7288,12 @@
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7303,47 +7307,277 @@
       <c r="T58" s="2" t="inlineStr"/>
       <c r="U58" s="2" t="inlineStr">
         <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
           <t>15:20</t>
         </is>
       </c>
-      <c r="V58" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W58" s="2" t="inlineStr">
+      <c r="W59" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X58" s="2" t="inlineStr">
+      <c r="X59" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y58" s="2" t="inlineStr">
+      <c r="Y59" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z58" s="2" t="inlineStr">
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
+      <c r="AA59" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB58" s="2" t="inlineStr">
+      <c r="AB59" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
         </is>
       </c>
-      <c r="AC58" s="2" t="inlineStr">
+      <c r="AC59" s="2" t="inlineStr">
         <is>
           <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,14 +2612,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,14 +4155,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,12 +4279,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5707,12 +5707,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6112,24 +6112,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6231,24 +6231,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,22 +6297,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6340,32 +6340,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6373,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6397,17 +6401,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6417,12 +6421,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6455,32 +6459,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -6488,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6512,17 +6520,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6532,12 +6540,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6570,32 +6578,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6603,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6627,17 +6639,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6647,12 +6659,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6718,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6800,32 +6812,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -6833,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6857,37 +6873,37 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6964,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7002,7 +7018,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7112,7 +7128,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7178,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7293,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7347,7 +7363,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7408,7 +7424,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7452,12 +7468,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7470,22 +7486,22 @@
       <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7518,12 +7534,12 @@
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7537,47 +7553,507 @@
       <c r="T60" s="2" t="inlineStr"/>
       <c r="U60" s="2" t="inlineStr">
         <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
           <t>15:40</t>
         </is>
       </c>
-      <c r="V60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W60" s="2" t="inlineStr">
+      <c r="W61" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X60" s="2" t="inlineStr">
+      <c r="X61" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y60" s="2" t="inlineStr">
+      <c r="Y61" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z60" s="2" t="inlineStr">
+      <c r="Z61" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr">
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
         </is>
       </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>9/15</t>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC64"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,17 +2017,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,14 +2850,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>83.3</t>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,14 +4631,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>83.3</t>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,22 +4869,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,17 +5226,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,14 +5583,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>83.3</t>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,17 +6059,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6697,32 +6697,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -6730,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6754,37 +6758,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6822,24 +6826,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6849,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6898,7 +6902,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6931,32 +6935,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6964,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6988,37 +6996,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7046,32 +7054,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7079,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7103,17 +7115,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7123,12 +7135,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7161,32 +7173,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7194,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7218,32 +7234,32 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7276,32 +7292,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -7309,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7333,37 +7353,37 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7391,32 +7411,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7424,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7448,17 +7472,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7468,12 +7492,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7539,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7578,7 +7602,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7654,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7708,7 +7732,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7823,7 +7847,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7908,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7938,7 +7962,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7999,7 +8023,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8048,12 +8072,1047 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
           <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>81.2</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,17 +2969,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,22 +3917,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,22 +4155,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,17 +4274,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,17 +4631,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,17 +4750,17 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,22 +4869,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,17 +5583,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,17 +5702,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,22 +6297,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,17 +6535,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,22 +6654,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,17 +6892,17 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7011,22 +7011,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7314,12 +7314,12 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7433,12 +7433,12 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7530,32 +7530,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -7563,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7587,17 +7591,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7607,12 +7611,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7645,32 +7649,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7678,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7702,37 +7710,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7760,32 +7768,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -7793,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7817,37 +7829,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7875,32 +7887,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7908,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7932,37 +7948,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7990,32 +8006,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -8023,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8047,32 +8067,32 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8105,32 +8125,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -8138,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8162,32 +8186,32 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8220,32 +8244,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -8253,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8277,32 +8305,32 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8335,32 +8363,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8368,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8392,37 +8424,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8598,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8713,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8767,7 +8799,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8828,7 +8860,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8943,7 +8975,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8997,7 +9029,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9005,22 +9037,22 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9053,12 +9085,12 @@
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9072,47 +9104,1082 @@
       <c r="T73" s="2" t="inlineStr"/>
       <c r="U73" s="2" t="inlineStr">
         <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="V73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr">
+      <c r="W74" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
+      <c r="Y74" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
         <is>
           <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>81.4</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,12 +2731,12 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,17 +3207,17 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,17 +3679,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,17 +3798,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,22 +4036,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,17 +4512,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,17 +4988,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,22 +6059,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,12 +6178,12 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6773,22 +6773,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7021,12 +7021,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7130,12 +7130,12 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,22 +7249,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,22 +7368,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,17 +7487,17 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8373,24 +8373,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8482,32 +8482,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -8515,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8539,37 +8543,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8597,32 +8601,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8630,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8654,32 +8662,32 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8712,32 +8720,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8745,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8769,37 +8781,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8827,32 +8839,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8860,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8884,32 +8900,32 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8942,32 +8958,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -8975,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8999,37 +9019,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -9057,32 +9077,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9090,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9114,27 +9138,27 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
@@ -9172,32 +9196,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -9205,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9229,27 +9257,27 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
@@ -9320,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9359,7 +9387,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9374,7 +9402,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9430,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9435,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9459,32 +9491,32 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9550,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9604,7 +9636,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9704,7 +9736,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9780,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9895,7 +9927,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10010,7 +10042,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10072,22 +10104,22 @@
       <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>18:01</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10120,12 +10152,12 @@
       <c r="M82" s="2" t="inlineStr"/>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10139,45 +10171,1195 @@
       <c r="T82" s="2" t="inlineStr"/>
       <c r="U82" s="2" t="inlineStr">
         <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
           <t>18:01</t>
         </is>
       </c>
-      <c r="V82" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W82" s="2" t="inlineStr">
+      <c r="W84" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X82" s="2" t="inlineStr">
+      <c r="X84" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y82" s="2" t="inlineStr">
+      <c r="Y84" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z82" s="2" t="inlineStr">
+      <c r="Z84" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
+      <c r="AA84" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AB82" s="2" t="inlineStr">
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>9/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>80.6</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>10/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="AC82" s="2" t="inlineStr">
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>75.8</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>3/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>12/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
         <is>
           <t>6/15</t>
         </is>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,17 +3798,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4874,17 +4874,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,17 +4988,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5945,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6302,12 +6302,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6659,7 +6659,7 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6778,17 +6778,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,22 +6892,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8082,22 +8082,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8444,17 +8444,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8563,17 +8563,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8677,17 +8677,17 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8915,7 +8915,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9049,7 +9049,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9315,32 +9315,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -9348,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9372,17 +9376,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9392,12 +9396,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9467,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9582,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9621,7 +9625,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9664,32 +9668,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9697,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9721,17 +9729,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9741,7 +9749,7 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
@@ -9751,7 +9759,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9851,7 +9859,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9927,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9981,7 +9989,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -10009,32 +10017,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -10042,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10066,37 +10078,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA81" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -10124,32 +10136,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -10157,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10181,17 +10197,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10201,17 +10217,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -10239,32 +10255,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10272,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10296,32 +10316,32 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10354,32 +10374,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10387,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10411,17 +10435,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10431,17 +10455,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10541,7 +10565,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10617,7 +10641,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10732,7 +10756,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10771,7 +10795,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10786,7 +10810,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10901,7 +10925,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10986,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11001,7 +11025,7 @@
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA89" s="2" t="inlineStr">
@@ -11077,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11192,7 +11216,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11236,12 +11260,12 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11254,22 +11278,22 @@
       <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -11302,12 +11326,12 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11356,12 +11380,817 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>11/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
           <t>80.0</t>
         </is>
       </c>
-      <c r="AC92" s="2" t="inlineStr">
-        <is>
-          <t>6/15</t>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>7/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>78.6</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>5/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>4/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>2/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3684,17 +3684,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5112,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,14 +5940,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6183,17 +6183,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6302,12 +6302,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6421,17 +6421,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6659,17 +6659,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6773,14 +6773,14 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6897,17 +6897,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7135,17 +7135,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7373,17 +7373,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7730,17 +7730,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7968,17 +7968,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8087,17 +8087,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8320,7 +8320,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8558,14 +8558,14 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9158,17 +9158,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9515,17 +9515,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9630,17 +9630,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9749,17 +9749,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10098,17 +10098,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10212,14 +10212,14 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10526,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10723,32 +10723,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -10756,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10780,17 +10784,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10800,17 +10804,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -10838,32 +10842,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10871,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10895,17 +10903,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10915,17 +10923,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10953,32 +10961,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -10986,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11010,17 +11022,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11030,12 +11042,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11068,32 +11080,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11101,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11125,17 +11141,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11145,17 +11161,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>2/15</t>
         </is>
       </c>
     </row>
@@ -11183,32 +11199,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>08:00</t>
@@ -11216,7 +11236,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11240,17 +11260,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11260,12 +11280,12 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11298,32 +11318,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -11331,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11355,17 +11379,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11375,17 +11399,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11413,32 +11437,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -11446,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11470,17 +11498,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11490,17 +11518,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11589,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11676,7 +11704,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11791,7 +11819,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11845,7 +11873,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>2/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -11873,32 +11901,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -11906,7 +11938,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11930,17 +11962,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11950,17 +11982,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -11968,22 +12000,22 @@
       <c r="A98" s="2" t="inlineStr"/>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>20:10</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -12016,12 +12048,12 @@
       <c r="M98" s="2" t="inlineStr"/>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12035,7 +12067,7 @@
       <c r="T98" s="2" t="inlineStr"/>
       <c r="U98" s="2" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="V98" s="2" t="inlineStr">
@@ -12065,17 +12097,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -12083,22 +12115,22 @@
       <c r="A99" s="2" t="inlineStr"/>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>20:40</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -12131,12 +12163,12 @@
       <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12150,47 +12182,507 @@
       <c r="T99" s="2" t="inlineStr"/>
       <c r="U99" s="2" t="inlineStr">
         <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
           <t>20:40</t>
         </is>
       </c>
-      <c r="V99" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W99" s="2" t="inlineStr">
+      <c r="W101" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X99" s="2" t="inlineStr">
+      <c r="X101" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y99" s="2" t="inlineStr">
+      <c r="Y101" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z99" s="2" t="inlineStr">
+      <c r="Z101" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA99" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>74.2</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
         <is>
           <t>1/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>13/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>8/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1670,12 +1670,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5707,17 +5707,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5945,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6778,17 +6778,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8206,17 +8206,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8563,17 +8563,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9039,12 +9039,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9864,17 +9864,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10217,17 +10217,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10760,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10804,12 +10804,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11328,24 +11328,24 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N92" s="2" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11404,7 +11404,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11447,24 +11447,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11523,12 +11523,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11556,32 +11556,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -11589,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11613,17 +11617,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11633,17 +11637,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -11911,24 +11915,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>20:56</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11938,7 +11942,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11987,7 +11991,7 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -12020,32 +12024,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -12053,7 +12061,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12077,17 +12085,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12097,12 +12105,12 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12135,32 +12143,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>12:00</t>
@@ -12168,7 +12180,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12192,17 +12204,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12212,17 +12224,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -12250,32 +12262,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>07:50</t>
@@ -12283,7 +12299,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12307,17 +12323,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12327,12 +12343,12 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12398,7 +12414,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12513,7 +12529,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12557,12 +12573,12 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
@@ -12628,7 +12644,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12672,17 +12688,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7611,12 +7611,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9044,12 +9044,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -10998,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11996,7 +11996,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>14/15</t>
+          <t>15/15</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12180,7 +12180,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12272,24 +12272,24 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12348,12 +12348,12 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>15/15</t>
+          <t>14/15</t>
         </is>
       </c>
     </row>
@@ -12381,32 +12381,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -12414,7 +12418,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12438,17 +12442,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12458,12 +12462,12 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
@@ -12529,7 +12533,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12644,7 +12648,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">

--- a/data/export/2026-10-04-浦东78路.xlsx
+++ b/data/export/2026-10-04-浦东78路.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5588,17 +5588,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8325,17 +8325,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -9233,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9979,17 +9979,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10933,7 +10933,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>12/15</t>
         </is>
       </c>
     </row>
@@ -10998,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>12/15</t>
+          <t>13/15</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12061,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12105,17 +12105,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12391,24 +12391,24 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
@@ -12500,32 +12500,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -12533,7 +12537,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12557,17 +12561,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12577,17 +12581,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>13/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -12648,7 +12652,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
